--- a/Saj_Ademir_codigo/Excel_leitura/processos.xlsx
+++ b/Saj_Ademir_codigo/Excel_leitura/processos.xlsx
@@ -1,31 +1,303 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="Y:\DIAFI-PRE-TRIAGEM\Arthur\Repos_\Naj_\Saj_Ademir_codigo\Excel_leitura\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505"/>
   </bookViews>
   <sheets>
     <sheet name="Plan1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="93">
+  <si>
+    <t>0016103-48.2017.4.03.6182</t>
+  </si>
+  <si>
+    <t>5004769-70.2020.4.03.6102</t>
+  </si>
+  <si>
+    <t>5002910-23.2019.4.03.6112</t>
+  </si>
   <si>
     <t>0003857-45.2014.8.26.0493</t>
   </si>
   <si>
+    <t>5008539-93.2018.4.03.6182</t>
+  </si>
+  <si>
+    <t>0511671-66.1993.4.03.6182</t>
+  </si>
+  <si>
+    <t>0032828-35.2005.4.03.6182</t>
+  </si>
+  <si>
+    <t>0006222-28.2009.4.03.6182</t>
+  </si>
+  <si>
+    <t>5001610-16.2020.4.03.6104</t>
+  </si>
+  <si>
+    <t>5006089-52.2020.4.03.6104</t>
+  </si>
+  <si>
+    <t>0005724-30.2013.403.6104</t>
+  </si>
+  <si>
+    <t>0001009-08.2014.4.03.6104</t>
+  </si>
+  <si>
+    <t>5007197-87.2018.4.03.6104</t>
+  </si>
+  <si>
+    <t>0001067-24.2009.4.03.6124</t>
+  </si>
+  <si>
+    <t>0000342-64.2011.4.03.6124</t>
+  </si>
+  <si>
+    <t>0001251-04.2014.4.03.6124</t>
+  </si>
+  <si>
+    <t>5000880-42.2020.4.03.6124</t>
+  </si>
+  <si>
+    <t>0001559-11.2012.4.03.6124</t>
+  </si>
+  <si>
+    <t>5001148-67.2018.4.03.6124</t>
+  </si>
+  <si>
+    <t>1004860-39.2014.8.26.0292</t>
+  </si>
+  <si>
+    <t>5005146-09.2018.4.03.6103</t>
+  </si>
+  <si>
+    <t>0001346-97.2014.4.03.6103</t>
+  </si>
+  <si>
+    <t>0006794-11.2015.4.03.6105</t>
+  </si>
+  <si>
+    <t>5010680-54.2020.4.03.6105</t>
+  </si>
+  <si>
+    <t>5017047-31.2019.4.03.6105</t>
+  </si>
+  <si>
+    <t>5008464-91.2018.4.03.6105</t>
+  </si>
+  <si>
+    <t>0020104-50.2016.4.03.6105</t>
+  </si>
+  <si>
+    <t>5011116-13.2020.4.03.6105</t>
+  </si>
+  <si>
+    <t>5000062-16.2021.4.03.6105</t>
+  </si>
+  <si>
+    <t>0010974-41.2013.4.03.6105</t>
+  </si>
+  <si>
+    <t>5007089-11.2020.4.03.6000</t>
+  </si>
+  <si>
+    <t>5003913-55.2020.4.03.6119</t>
+  </si>
+  <si>
+    <t>5005303-94.2019.4.03.6119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5006389-37.2018.403.6119 </t>
+  </si>
+  <si>
+    <t>5002950-88.2018.4.03.6128</t>
+  </si>
+  <si>
+    <t>0006987-88.2014.4.03.6128</t>
+  </si>
+  <si>
+    <t>0002272-03.2014.4.03.6128</t>
+  </si>
+  <si>
+    <t>0001903-72.2015.4.03.6128</t>
+  </si>
+  <si>
+    <t>5004570-32.2018.4.03.6130</t>
+  </si>
+  <si>
+    <t>0002180-48.2016.4.03.6130</t>
+  </si>
+  <si>
+    <t>0011856-98.2012.8.26.0176</t>
+  </si>
+  <si>
+    <t>5002735-38.2020.4.03.6130</t>
+  </si>
+  <si>
+    <t>5003244-03.2019.4.03.6130</t>
+  </si>
+  <si>
+    <t>5005525-79.2020.403.6102</t>
+  </si>
+  <si>
+    <t>5006442-35.2019.403.6102</t>
+  </si>
+  <si>
+    <t>5007282-45.2019.4.03.6102</t>
+  </si>
+  <si>
+    <t>5004666-63.2020.4.03.6102</t>
+  </si>
+  <si>
+    <t>5002151-55.2020.4.03.6102</t>
+  </si>
+  <si>
+    <t>0057734-06.2016.4.03.6182</t>
+  </si>
+  <si>
+    <t>0001863-06.2007.4.03.6182</t>
+  </si>
+  <si>
+    <t>0033818-26.2005.4.03.6182</t>
+  </si>
+  <si>
+    <t>0028400-92.2014.4.03.6182</t>
+  </si>
+  <si>
+    <t>0517523-03.1995.4.03.6182</t>
+  </si>
+  <si>
+    <t>0020970-89.2014.4.03.6182</t>
+  </si>
+  <si>
+    <t>0055449-89.2006.4.03.6182</t>
+  </si>
+  <si>
+    <t>0502025-66.1992.4.03.6182</t>
+  </si>
+  <si>
+    <t>0013153-66.2017.4.03.6182</t>
+  </si>
+  <si>
+    <t>0059694-90.1999.4.03.6182</t>
+  </si>
+  <si>
+    <t>0034064-70.2015.4.03.6182</t>
+  </si>
+  <si>
+    <t>0000771-38.2020.826.0596</t>
+  </si>
+  <si>
+    <t>0005786-71.2016.4.03.6102</t>
+  </si>
+  <si>
+    <t>0005456-74.2016.4.03.6102</t>
+  </si>
+  <si>
+    <t>0003126-92.2013.4.03.6140</t>
+  </si>
+  <si>
+    <t>5001440-04.2018.4.03.6140</t>
+  </si>
+  <si>
+    <t>0003179-13.2016.4.03.6126</t>
+  </si>
+  <si>
     <t>0001182-58.2017.4.03.6126</t>
   </si>
   <si>
-    <t>0502025-66.1992.4.03.6182</t>
+    <t>5001355-47.2020.4.03.6140</t>
+  </si>
+  <si>
+    <t>5003226-57.2020.4.03.6126</t>
+  </si>
+  <si>
+    <t>5000679-02.2020.4.03.6140</t>
+  </si>
+  <si>
+    <t>5004950-96.2020.4.03.6126</t>
+  </si>
+  <si>
+    <t>5004735-59.2020.403.6114</t>
+  </si>
+  <si>
+    <t>5004563-20.2020.403.6114</t>
+  </si>
+  <si>
+    <t>5004061-42.2019.4.03.6106</t>
+  </si>
+  <si>
+    <t>5002146-21.2020.4.03.6106</t>
   </si>
   <si>
     <t>5000113-65.2020.4.03.6136</t>
+  </si>
+  <si>
+    <t>5000560-53.2020.4.03.6136</t>
+  </si>
+  <si>
+    <t>0001042-29.2012.8.26.0337</t>
+  </si>
+  <si>
+    <t>5000196-87.2020.4.03.6134</t>
+  </si>
+  <si>
+    <t>5002747-18.2020.4.03.6109</t>
+  </si>
+  <si>
+    <t>5001750-35.2020.4.03.6109</t>
+  </si>
+  <si>
+    <t>5002814-46.2018.4.03.6143</t>
+  </si>
+  <si>
+    <t>0003089-27.2014.4.03.6109</t>
+  </si>
+  <si>
+    <t>0005648-83.2016.4.03.6109</t>
+  </si>
+  <si>
+    <t>0007691-90.2016.4.03.6109</t>
+  </si>
+  <si>
+    <t>0006600-38.2011.4.03.6109</t>
+  </si>
+  <si>
+    <t>0010386-90.2011.4.03.6109</t>
+  </si>
+  <si>
+    <t>5006402-66.2018.4.03.6109</t>
+  </si>
+  <si>
+    <t>0001925-22.2017.4.03.6109</t>
+  </si>
+  <si>
+    <t>5001400-72.2019.4.03.6112</t>
+  </si>
+  <si>
+    <t>5005614-43.2018.4.03.6112</t>
+  </si>
+  <si>
+    <t>5001401-57.2019.4.03.6112</t>
+  </si>
+  <si>
+    <t>5001301-68.2020.4.03.6112</t>
+  </si>
+  <si>
+    <t>5000458-06.2020.4.03.6112</t>
   </si>
 </sst>
 </file>
@@ -61,14 +333,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -81,9 +355,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema do Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Escritório">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -121,9 +395,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Escritório">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -158,7 +432,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -193,7 +467,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Escritório">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -214,7 +488,6 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
                 <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
@@ -225,31 +498,31 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
+                <a:tint val="51000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
+                <a:tint val="15000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
+                <a:tint val="94000"/>
                 <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
+              <a:shade val="9500"/>
               <a:satMod val="105000"/>
             </a:schemeClr>
           </a:solidFill>
@@ -271,7 +544,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -329,7 +602,7 @@
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
+                <a:tint val="20000"/>
                 <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
@@ -342,13 +615,12 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
                 <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
+                <a:tint val="80000"/>
                 <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
@@ -367,30 +639,518 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A4"/>
+  <sheetPr>
+    <outlinePr summaryBelow="0"/>
+  </sheetPr>
+  <dimension ref="A1:A101"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="24.42578125" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="4" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="1" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A34" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A35" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="1" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="1" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A39" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A40" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A43" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A44" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A52" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="1" t="s">
         <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A59" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A60" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A61" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A62" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A63" s="1" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A64" s="1" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A66" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A67" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A68" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A69" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A70" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A71" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A72" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A73" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A74" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A80" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A81" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A83" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A84" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A85" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A86" s="1" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A87" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A88" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A90" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A91" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A96" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A97" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A100" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A101" s="1" t="s">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
